--- a/Team-Data/2008-09/3-1-2008-09.xlsx
+++ b/Team-Data/2008-09/3-1-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,43 +728,43 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
         <v>33</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.569</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K2" t="n">
         <v>0.456</v>
       </c>
       <c r="L2" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M2" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="N2" t="n">
         <v>0.365</v>
       </c>
       <c r="O2" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P2" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="Q2" t="n">
         <v>0.736</v>
@@ -712,13 +779,13 @@
         <v>40</v>
       </c>
       <c r="U2" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V2" t="n">
         <v>13.1</v>
       </c>
       <c r="W2" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X2" t="n">
         <v>4.7</v>
@@ -733,46 +800,46 @@
         <v>20.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN2" t="n">
         <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP2" t="n">
         <v>11</v>
@@ -781,16 +848,16 @@
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV2" t="n">
         <v>7</v>
@@ -811,7 +878,7 @@
         <v>17</v>
       </c>
       <c r="BB2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -846,19 +913,19 @@
         <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>0.767</v>
+        <v>0.783</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
         <v>77.09999999999999</v>
@@ -873,34 +940,34 @@
         <v>16.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.392</v>
+        <v>0.393</v>
       </c>
       <c r="O3" t="n">
         <v>20.2</v>
       </c>
       <c r="P3" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
         <v>42.7</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V3" t="n">
         <v>15.9</v>
       </c>
       <c r="W3" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X3" t="n">
         <v>4.8</v>
@@ -915,13 +982,13 @@
         <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.7</v>
+        <v>101.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -951,37 +1018,37 @@
         <v>20</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW3" t="n">
         <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-1.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="n">
         <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
         <v>2</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>23</v>
@@ -1139,13 +1206,13 @@
         <v>25</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ4" t="n">
         <v>28</v>
       </c>
       <c r="AR4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
         <v>27</v>
@@ -1163,7 +1230,7 @@
         <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1178,7 +1245,7 @@
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
         <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.441</v>
+        <v>0.45</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
@@ -1225,10 +1292,10 @@
         <v>37.7</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L5" t="n">
         <v>5.9</v>
@@ -1237,34 +1304,34 @@
         <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O5" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.788</v>
+        <v>0.787</v>
       </c>
       <c r="R5" t="n">
         <v>12.1</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
         <v>42.4</v>
       </c>
       <c r="U5" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
@@ -1276,16 +1343,16 @@
         <v>21.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.7</v>
+        <v>100.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.7</v>
+        <v>-1.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1297,16 +1364,16 @@
         <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL5" t="n">
         <v>24</v>
@@ -1318,10 +1385,10 @@
         <v>10</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1339,7 +1406,7 @@
         <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW5" t="n">
         <v>11</v>
@@ -1348,13 +1415,13 @@
         <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB5" t="n">
         <v>11</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -1392,43 +1459,43 @@
         <v>57</v>
       </c>
       <c r="E6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.789</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J6" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="O6" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P6" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R6" t="n">
         <v>10.8</v>
@@ -1440,10 +1507,10 @@
         <v>41.8</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V6" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
@@ -1452,40 +1519,40 @@
         <v>5.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
         <v>20.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.3</v>
+        <v>100.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2</v>
       </c>
-      <c r="AF6" t="n">
-        <v>1</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
@@ -1494,28 +1561,28 @@
         <v>3</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN6" t="n">
         <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ6" t="n">
         <v>22</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
         <v>24</v>
@@ -1530,13 +1597,13 @@
         <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="n">
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1638,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
         <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>0.61</v>
+        <v>0.603</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J7" t="n">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="K7" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L7" t="n">
         <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O7" t="n">
         <v>18.1</v>
@@ -1613,19 +1680,19 @@
         <v>0.8169999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U7" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V7" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W7" t="n">
         <v>7.3</v>
@@ -1637,19 +1704,19 @@
         <v>4.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA7" t="n">
         <v>19.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.2</v>
+        <v>101</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1679,7 +1746,7 @@
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
         <v>24</v>
@@ -1691,28 +1758,28 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
         <v>7</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>6</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" t="n">
         <v>39</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>0.65</v>
+        <v>0.661</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
@@ -1771,10 +1838,10 @@
         <v>36.7</v>
       </c>
       <c r="J8" t="n">
-        <v>78.5</v>
+        <v>78.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.468</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="n">
         <v>6.4</v>
@@ -1783,7 +1850,7 @@
         <v>17.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O8" t="n">
         <v>23.1</v>
@@ -1792,46 +1859,46 @@
         <v>30.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R8" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S8" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T8" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V8" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y8" t="n">
         <v>5.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA8" t="n">
         <v>23.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>102.9</v>
+        <v>103.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1843,13 +1910,13 @@
         <v>6</v>
       </c>
       <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>25</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>24</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1873,13 +1940,13 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
         <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
@@ -1903,7 +1970,7 @@
         <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="n">
         <v>9</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
         <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.491</v>
       </c>
       <c r="H9" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J9" t="n">
-        <v>78.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L9" t="n">
         <v>4.6</v>
@@ -1965,64 +2032,64 @@
         <v>13.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="O9" t="n">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
       <c r="P9" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.749</v>
+        <v>0.745</v>
       </c>
       <c r="R9" t="n">
         <v>10.8</v>
       </c>
       <c r="S9" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T9" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U9" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V9" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X9" t="n">
         <v>4.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z9" t="n">
         <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.2</v>
+        <v>93</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
         <v>14</v>
@@ -2043,25 +2110,25 @@
         <v>28</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
         <v>23</v>
@@ -2073,7 +2140,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY9" t="n">
         <v>4</v>
@@ -2082,7 +2149,7 @@
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
@@ -2135,10 +2202,10 @@
         <v>39.3</v>
       </c>
       <c r="J10" t="n">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L10" t="n">
         <v>6.7</v>
@@ -2147,13 +2214,13 @@
         <v>17.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="O10" t="n">
         <v>22.8</v>
       </c>
       <c r="P10" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="Q10" t="n">
         <v>0.783</v>
@@ -2171,31 +2238,31 @@
         <v>20.8</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="W10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA10" t="n">
         <v>23.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.1</v>
+        <v>108.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2216,16 +2283,16 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM10" t="n">
         <v>17</v>
       </c>
       <c r="AN10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -2243,13 +2310,13 @@
         <v>15</v>
       </c>
       <c r="AT10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU10" t="n">
         <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>4</v>
@@ -2258,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -2299,97 +2366,97 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
         <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>0.633</v>
+        <v>0.627</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J11" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K11" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M11" t="n">
         <v>20.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O11" t="n">
         <v>19.5</v>
       </c>
       <c r="P11" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S11" t="n">
         <v>32.3</v>
       </c>
       <c r="T11" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U11" t="n">
         <v>20.5</v>
       </c>
       <c r="V11" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W11" t="n">
         <v>6.9</v>
       </c>
       <c r="X11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y11" t="n">
         <v>5.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA11" t="n">
         <v>20.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>26</v>
@@ -2404,13 +2471,13 @@
         <v>6</v>
       </c>
       <c r="AM11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN11" t="n">
         <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2419,7 +2486,7 @@
         <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2431,10 +2498,10 @@
         <v>19</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
@@ -2446,13 +2513,13 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -2481,34 +2548,34 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
         <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>0.419</v>
+        <v>0.41</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J12" t="n">
-        <v>86.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L12" t="n">
         <v>7.9</v>
       </c>
       <c r="M12" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N12" t="n">
         <v>0.373</v>
@@ -2520,22 +2587,22 @@
         <v>23.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.805</v>
+        <v>0.806</v>
       </c>
       <c r="R12" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S12" t="n">
         <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U12" t="n">
         <v>22.2</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W12" t="n">
         <v>6.9</v>
@@ -2544,7 +2611,7 @@
         <v>5.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
         <v>23.8</v>
@@ -2553,22 +2620,22 @@
         <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.6</v>
+        <v>104.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
         <v>8</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL12" t="n">
         <v>5</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
         <v>17</v>
@@ -2598,7 +2665,7 @@
         <v>21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR12" t="n">
         <v>11</v>
@@ -2613,16 +2680,16 @@
         <v>5</v>
       </c>
       <c r="AV12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW12" t="n">
         <v>22</v>
       </c>
-      <c r="AW12" t="n">
-        <v>25</v>
-      </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2634,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>26</v>
@@ -2753,10 +2820,10 @@
         <v>27</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2774,16 +2841,16 @@
         <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ13" t="n">
         <v>26</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS13" t="n">
         <v>24</v>
@@ -2795,7 +2862,7 @@
         <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
         <v>17</v>
@@ -2807,10 +2874,10 @@
         <v>22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -2848,13 +2915,13 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>0.797</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,7 +2930,7 @@
         <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="K14" t="n">
         <v>0.477</v>
@@ -2872,10 +2939,10 @@
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.363</v>
+        <v>0.367</v>
       </c>
       <c r="O14" t="n">
         <v>20.6</v>
@@ -2884,16 +2951,16 @@
         <v>26.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R14" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S14" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T14" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U14" t="n">
         <v>23.7</v>
@@ -2902,37 +2969,37 @@
         <v>13.7</v>
       </c>
       <c r="W14" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X14" t="n">
         <v>5.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="AA14" t="n">
         <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>109.1</v>
+        <v>108.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>16</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2962,13 +3029,13 @@
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2983,16 +3050,16 @@
         <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3147,13 +3214,13 @@
         <v>24</v>
       </c>
       <c r="AR15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
         <v>26</v>
       </c>
       <c r="AT15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
@@ -3165,7 +3232,7 @@
         <v>8</v>
       </c>
       <c r="AX15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY15" t="n">
         <v>25</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3308,7 +3375,7 @@
         <v>12</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3320,10 +3387,10 @@
         <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ16" t="n">
         <v>23</v>
@@ -3338,22 +3405,22 @@
         <v>29</v>
       </c>
       <c r="AU16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
         <v>5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
         <v>28</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
         <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>0.475</v>
+        <v>0.468</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3412,7 +3479,7 @@
         <v>81.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L17" t="n">
         <v>6.1</v>
@@ -3421,31 +3488,31 @@
         <v>16.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="P17" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R17" t="n">
         <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
         <v>7.2</v>
@@ -3457,25 +3524,25 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="AA17" t="n">
         <v>23.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>15</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3499,13 +3566,13 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3517,13 +3584,13 @@
         <v>25</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -3573,22 +3640,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>0.305</v>
+        <v>0.31</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J18" t="n">
         <v>83.5</v>
@@ -3597,34 +3664,34 @@
         <v>0.443</v>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M18" t="n">
         <v>18.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O18" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="P18" t="n">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R18" t="n">
         <v>12.3</v>
       </c>
       <c r="S18" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U18" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V18" t="n">
         <v>14.5</v>
@@ -3642,16 +3709,16 @@
         <v>21.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-4.4</v>
+        <v>-4.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,16 +3730,16 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL18" t="n">
         <v>20</v>
@@ -3684,13 +3751,13 @@
         <v>27</v>
       </c>
       <c r="AO18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP18" t="n">
         <v>14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
         <v>5</v>
@@ -3699,10 +3766,10 @@
         <v>19</v>
       </c>
       <c r="AT18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
         <v>16</v>
@@ -3720,10 +3787,10 @@
         <v>20</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
         <v>26</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>0.441</v>
+        <v>0.448</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
@@ -3785,28 +3852,28 @@
         <v>20.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.376</v>
+        <v>0.378</v>
       </c>
       <c r="O19" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P19" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="R19" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S19" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T19" t="n">
         <v>40.5</v>
       </c>
       <c r="U19" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V19" t="n">
         <v>13.3</v>
@@ -3824,25 +3891,25 @@
         <v>22.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC19" t="n">
         <v>-2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
@@ -3854,7 +3921,7 @@
         <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
         <v>7</v>
@@ -3863,13 +3930,13 @@
         <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
         <v>10</v>
@@ -3878,10 +3945,10 @@
         <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU19" t="n">
         <v>28</v>
@@ -3890,10 +3957,10 @@
         <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY19" t="n">
         <v>17</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -3937,58 +4004,58 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F20" t="n">
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.621</v>
+        <v>0.614</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
       </c>
       <c r="I20" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J20" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
         <v>7.5</v>
       </c>
       <c r="M20" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="O20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="R20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="U20" t="n">
         <v>19.9</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="O20" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="P20" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="R20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="S20" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="T20" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>19.8</v>
       </c>
       <c r="V20" t="n">
         <v>12.6</v>
@@ -3997,10 +4064,10 @@
         <v>7.3</v>
       </c>
       <c r="X20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z20" t="n">
         <v>20.7</v>
@@ -4009,25 +4076,25 @@
         <v>21</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC20" t="n">
         <v>2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE20" t="n">
         <v>10</v>
       </c>
       <c r="AF20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG20" t="n">
         <v>9</v>
       </c>
       <c r="AH20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
         <v>28</v>
@@ -4036,55 +4103,55 @@
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM20" t="n">
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR20" t="n">
         <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO21" t="n">
         <v>23</v>
@@ -4245,7 +4312,7 @@
         <v>8</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
         <v>9</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-6</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
         <v>28</v>
@@ -4391,10 +4458,10 @@
         <v>28</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
@@ -4409,10 +4476,10 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP22" t="n">
         <v>8</v>
@@ -4427,7 +4494,7 @@
         <v>11</v>
       </c>
       <c r="AT22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU22" t="n">
         <v>20</v>
@@ -4442,13 +4509,13 @@
         <v>21</v>
       </c>
       <c r="AY22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ22" t="n">
         <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>6.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,13 +4640,13 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
         <v>22</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
         <v>9</v>
@@ -4591,13 +4658,13 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
         <v>10</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4755,7 +4822,7 @@
         <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI24" t="n">
         <v>18</v>
@@ -4806,7 +4873,7 @@
         <v>8</v>
       </c>
       <c r="AY24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ24" t="n">
         <v>7</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F25" t="n">
         <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>0.576</v>
+        <v>0.569</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="J25" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.502</v>
+        <v>0.501</v>
       </c>
       <c r="L25" t="n">
         <v>6.4</v>
@@ -4877,25 +4944,25 @@
         <v>16.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="O25" t="n">
         <v>20.9</v>
       </c>
       <c r="P25" t="n">
-        <v>27.6</v>
+        <v>27.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.76</v>
+        <v>0.764</v>
       </c>
       <c r="R25" t="n">
         <v>10.2</v>
       </c>
       <c r="S25" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T25" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U25" t="n">
         <v>22.6</v>
@@ -4904,7 +4971,7 @@
         <v>16.1</v>
       </c>
       <c r="W25" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X25" t="n">
         <v>4.9</v>
@@ -4913,19 +4980,19 @@
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>107.2</v>
+        <v>107</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4961,10 +5028,10 @@
         <v>4</v>
       </c>
       <c r="AP25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR25" t="n">
         <v>24</v>
@@ -4973,7 +5040,7 @@
         <v>9</v>
       </c>
       <c r="AT25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU25" t="n">
         <v>4</v>
@@ -4991,10 +5058,10 @@
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
         <v>3</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -5032,46 +5099,46 @@
         <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G26" t="n">
-        <v>0.638</v>
+        <v>0.621</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="P26" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S26" t="n">
         <v>28.3</v>
@@ -5086,49 +5153,49 @@
         <v>12.9</v>
       </c>
       <c r="W26" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X26" t="n">
         <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z26" t="n">
         <v>20.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5140,13 +5207,13 @@
         <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,31 +5222,31 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
         <v>17</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5380,7 @@
         <v>26</v>
       </c>
       <c r="AL27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM27" t="n">
         <v>15</v>
@@ -5322,7 +5389,7 @@
         <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP27" t="n">
         <v>13</v>
@@ -5340,10 +5407,10 @@
         <v>30</v>
       </c>
       <c r="AU27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV27" t="n">
         <v>26</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>27</v>
       </c>
       <c r="AW27" t="n">
         <v>18</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -5393,25 +5460,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E28" t="n">
         <v>39</v>
       </c>
       <c r="F28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>0.672</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J28" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K28" t="n">
         <v>0.464</v>
@@ -5420,34 +5487,34 @@
         <v>7.9</v>
       </c>
       <c r="M28" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="O28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="P28" t="n">
         <v>20.1</v>
       </c>
-      <c r="N28" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="O28" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="P28" t="n">
-        <v>20</v>
-      </c>
       <c r="Q28" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="T28" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U28" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V28" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="W28" t="n">
         <v>5.7</v>
@@ -5459,19 +5526,19 @@
         <v>4.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA28" t="n">
         <v>18.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5486,16 +5553,16 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ28" t="n">
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM28" t="n">
         <v>8</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5519,7 +5586,7 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -5546,7 +5613,7 @@
         <v>22</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -5575,64 +5642,64 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
         <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G29" t="n">
-        <v>0.377</v>
+        <v>0.383</v>
       </c>
       <c r="H29" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I29" t="n">
         <v>36.3</v>
       </c>
       <c r="J29" t="n">
-        <v>79.5</v>
+        <v>79.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M29" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="O29" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P29" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.83</v>
+        <v>0.828</v>
       </c>
       <c r="R29" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S29" t="n">
         <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="U29" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V29" t="n">
         <v>13.2</v>
       </c>
       <c r="W29" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X29" t="n">
         <v>4.8</v>
@@ -5644,16 +5711,16 @@
         <v>19.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB29" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5671,10 +5738,10 @@
         <v>19</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
         <v>22</v>
@@ -5683,7 +5750,7 @@
         <v>22</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO29" t="n">
         <v>19</v>
@@ -5701,10 +5768,10 @@
         <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV29" t="n">
         <v>8</v>
@@ -5722,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
         <v>21</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F30" t="n">
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>0.617</v>
+        <v>0.61</v>
       </c>
       <c r="H30" t="n">
         <v>48.3</v>
       </c>
       <c r="I30" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J30" t="n">
-        <v>79.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="K30" t="n">
-        <v>0.479</v>
+        <v>0.48</v>
       </c>
       <c r="L30" t="n">
         <v>4.9</v>
@@ -5787,7 +5854,7 @@
         <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
       <c r="O30" t="n">
         <v>21.7</v>
@@ -5796,10 +5863,10 @@
         <v>28.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R30" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S30" t="n">
         <v>29.2</v>
@@ -5808,19 +5875,19 @@
         <v>40.8</v>
       </c>
       <c r="U30" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="V30" t="n">
         <v>14.9</v>
       </c>
       <c r="W30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X30" t="n">
         <v>4.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Z30" t="n">
         <v>22.1</v>
@@ -5829,13 +5896,13 @@
         <v>23.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>103.1</v>
+        <v>103</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE30" t="n">
         <v>8</v>
@@ -5847,7 +5914,7 @@
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5883,22 +5950,22 @@
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ30" t="n">
         <v>21</v>
@@ -5907,10 +5974,10 @@
         <v>1</v>
       </c>
       <c r="BB30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6029,7 +6096,7 @@
         <v>28</v>
       </c>
       <c r="AH31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI31" t="n">
         <v>20</v>
@@ -6056,7 +6123,7 @@
         <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6080,10 +6147,10 @@
         <v>25</v>
       </c>
       <c r="AY31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-1-2008-09</t>
+          <t>2009-03-01</t>
         </is>
       </c>
     </row>
